--- a/assets/img/2024-07-01-Omnissa-poc/Omnissa-success-criteria.xlsx
+++ b/assets/img/2024-07-01-Omnissa-poc/Omnissa-success-criteria.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mbeaugrand/github/blog/assets/img/2024-07-01-Omnissa-poc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77C41C5-6EA7-7A4D-90D1-3F043025D44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91DA33F-0499-434A-99AA-8F006E3AA995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14480" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="861" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,18 @@
     <sheet name="Customer" sheetId="47" r:id="rId1"/>
     <sheet name="Stakeholders" sheetId="48" r:id="rId2"/>
     <sheet name="UEM" sheetId="43" r:id="rId3"/>
+    <sheet name="VDI" sheetId="49" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Customer!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">UEM!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">VDI!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Customer!$A$1:$B$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">UEM!$A$1:$D$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">VDI!$A$1:$D$50</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Customer!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">UEM!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">VDI!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,10 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="87">
-  <si>
-    <t>Location (ie. Regional, City &amp; QLD, NSW, VIC...)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="136">
   <si>
     <t>Industry</t>
   </si>
@@ -307,6 +308,156 @@
   </si>
   <si>
     <t>Omnissa</t>
+  </si>
+  <si>
+    <t>City, Country</t>
+  </si>
+  <si>
+    <t>VDI &amp; Application Delivery</t>
+  </si>
+  <si>
+    <t>Virtual desktops are provisioned and accessible to all pilot users based on defined personas</t>
+  </si>
+  <si>
+    <t>Published applications are delivered reliably across Horizon Client and browser access</t>
+  </si>
+  <si>
+    <t>All agreed business use cases are validated within the POC scope</t>
+  </si>
+  <si>
+    <t>Applications are successfully packaged and assigned using App Volumes</t>
+  </si>
+  <si>
+    <t>Dynamic application attachment occurs without requiring image rebuild</t>
+  </si>
+  <si>
+    <t>Application updates and rollback procedures are validated</t>
+  </si>
+  <si>
+    <t>Application delivery model reduces image management complexity</t>
+  </si>
+  <si>
+    <t>User settings persist across non-persistent sessions</t>
+  </si>
+  <si>
+    <t>Application personalization is retained without profile bloat</t>
+  </si>
+  <si>
+    <t>Logon performance is optimized through DEM configuration</t>
+  </si>
+  <si>
+    <t>Environment policies are applied consistently based on user context</t>
+  </si>
+  <si>
+    <t>Graphics &amp; Performance (GPU where applicable)</t>
+  </si>
+  <si>
+    <t>GPU-enabled desktop pools are successfully deployed</t>
+  </si>
+  <si>
+    <t>Graphics-intensive workloads perform within agreed SLA</t>
+  </si>
+  <si>
+    <t>Real-time collaboration and multimedia workloads perform without degradation</t>
+  </si>
+  <si>
+    <t>User feedback confirms acceptable visual and interaction experience</t>
+  </si>
+  <si>
+    <t>Hybrid / Cloud Architecture Validation</t>
+  </si>
+  <si>
+    <t>Horizon pods are integrated across on-premises and cloud environments (if in scope)</t>
+  </si>
+  <si>
+    <t>Cloud-hosted desktops are provisioned and accessible</t>
+  </si>
+  <si>
+    <t>User entitlements function consistently regardless of workload location</t>
+  </si>
+  <si>
+    <t>Cross-site or cross-pod failover scenarios are validated</t>
+  </si>
+  <si>
+    <t>User Experience &amp; Performance</t>
+  </si>
+  <si>
+    <t>Average desktop login time meets agreed performance threshold</t>
+  </si>
+  <si>
+    <t>Application launch time meets agreed SLA</t>
+  </si>
+  <si>
+    <t>Session stability is maintained under peak pilot load</t>
+  </si>
+  <si>
+    <t>End-user satisfaction survey reflects positive experience</t>
+  </si>
+  <si>
+    <t>Security &amp; Compliance</t>
+  </si>
+  <si>
+    <t>SSO and MFA integration is validated and enforced</t>
+  </si>
+  <si>
+    <t>Role-based administrative access is configured and verified</t>
+  </si>
+  <si>
+    <t>All sessions are encrypted and compliant with security standards</t>
+  </si>
+  <si>
+    <t>Audit logging and reporting meet compliance requirements</t>
+  </si>
+  <si>
+    <t>Scalability &amp; Resilience</t>
+  </si>
+  <si>
+    <t>Connection Servers are deployed with high availability</t>
+  </si>
+  <si>
+    <t>Load balancing across desktop pools is validated</t>
+  </si>
+  <si>
+    <t>Environment scales to expected concurrent user levels</t>
+  </si>
+  <si>
+    <t>Compute and storage utilization remain within acceptable thresholds</t>
+  </si>
+  <si>
+    <t>Operational Readiness</t>
+  </si>
+  <si>
+    <t>Image lifecycle and patching processes are documented and validated</t>
+  </si>
+  <si>
+    <t>Monitoring and alerting provide actionable operational insight</t>
+  </si>
+  <si>
+    <t>Support model and runbook are defined for BAU operations</t>
+  </si>
+  <si>
+    <t>Operations team confirms readiness to support production rollout</t>
+  </si>
+  <si>
+    <t>Go / No-Go Decision</t>
+  </si>
+  <si>
+    <t>All critical success criteria are met or have agreed remediation plans</t>
+  </si>
+  <si>
+    <t>Stakeholders formally approve progression to production phase</t>
+  </si>
+  <si>
+    <t>VDI success criteria</t>
+  </si>
+  <si>
+    <t>External access is secured and functional via a secure gateway</t>
+  </si>
+  <si>
+    <t>Application Lifecycle</t>
+  </si>
+  <si>
+    <t>User profile and data</t>
   </si>
 </sst>
 </file>
@@ -889,24 +1040,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -928,6 +1061,24 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="99">
     <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1030,7 +1181,37 @@
     <cellStyle name="Normal 2 3" xfId="28" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
     <cellStyle name="Normal 4" xfId="29" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1265,6 +1446,55 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E78C16F4-8897-7E4F-A1E6-5E5C2EC878A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="4254500" cy="1221257"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>4254500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1221257</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA4AB32D-197A-A341-A6BA-52D277CAC843}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1593,7 +1823,7 @@
     <row r="1" spans="1:37" ht="97" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="46"/>
       <c r="B1" s="48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1632,22 +1862,22 @@
       <c r="AK1" s="1"/>
     </row>
     <row r="2" spans="1:37" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59" t="s">
-        <v>13</v>
+      <c r="A2" s="54"/>
+      <c r="B2" s="55" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="7"/>
     </row>
     <row r="3" spans="1:37" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="50"/>
       <c r="C3" s="7"/>
     </row>
     <row r="4" spans="1:37" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="10"/>
@@ -1667,7 +1897,7 @@
     </row>
     <row r="5" spans="1:37" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="10"/>
@@ -1687,7 +1917,7 @@
     </row>
     <row r="6" spans="1:37" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="10"/>
@@ -1707,7 +1937,7 @@
     </row>
     <row r="7" spans="1:37" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="10"/>
@@ -1727,7 +1957,7 @@
     </row>
     <row r="8" spans="1:37" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="10"/>
@@ -1747,7 +1977,7 @@
     </row>
     <row r="9" spans="1:37" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="42"/>
       <c r="C9" s="10"/>
@@ -1766,10 +1996,10 @@
       <c r="P9" s="11"/>
     </row>
     <row r="10" spans="1:37" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="60" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="61"/>
+      <c r="A10" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="68"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1786,8 +2016,8 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:37" ht="215" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="54"/>
-      <c r="B11" s="55"/>
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -2624,7 +2854,7 @@
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
@@ -2662,22 +2892,22 @@
       <c r="AL1" s="22"/>
     </row>
     <row r="2" spans="1:39" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="57" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="63" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="62" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:39" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -3006,7 +3236,7 @@
     </row>
     <row r="11" spans="1:39" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" s="39"/>
       <c r="C11" s="39"/>
@@ -3252,10 +3482,10 @@
       <c r="AM16" s="24"/>
     </row>
     <row r="17" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="64"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="66"/>
+      <c r="A17" s="58"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="60"/>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
@@ -3271,9 +3501,9 @@
       <c r="Q17" s="22"/>
     </row>
     <row r="18" spans="1:17" s="21" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="56"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="56"/>
+      <c r="A18" s="69"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
       <c r="D18" s="32"/>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -4578,7 +4808,7 @@
       <c r="B1" s="44"/>
       <c r="C1" s="44"/>
       <c r="D1" s="52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -4617,23 +4847,23 @@
       <c r="AM1" s="1"/>
     </row>
     <row r="2" spans="1:39" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="67" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="67" t="s">
+      <c r="A2" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="67" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="67" t="s">
-        <v>10</v>
+      <c r="D2" s="61" t="s">
+        <v>9</v>
       </c>
       <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:39" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
@@ -4655,7 +4885,7 @@
     </row>
     <row r="4" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -4677,7 +4907,7 @@
     </row>
     <row r="5" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -4699,7 +4929,7 @@
     </row>
     <row r="6" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -4721,7 +4951,7 @@
     </row>
     <row r="7" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -4743,7 +4973,7 @@
     </row>
     <row r="8" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -4765,7 +4995,7 @@
     </row>
     <row r="9" spans="1:39" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -4787,7 +5017,7 @@
     </row>
     <row r="10" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -4809,7 +5039,7 @@
     </row>
     <row r="11" spans="1:39" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -4831,7 +5061,7 @@
     </row>
     <row r="12" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -4853,7 +5083,7 @@
     </row>
     <row r="13" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -4875,7 +5105,7 @@
     </row>
     <row r="14" spans="1:39" s="4" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -4897,7 +5127,7 @@
     </row>
     <row r="15" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -4919,7 +5149,7 @@
     </row>
     <row r="16" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -4941,7 +5171,7 @@
     </row>
     <row r="17" spans="1:18" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B17" s="33"/>
       <c r="C17" s="33"/>
@@ -4963,7 +5193,7 @@
     </row>
     <row r="18" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -4985,7 +5215,7 @@
     </row>
     <row r="19" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -5007,7 +5237,7 @@
     </row>
     <row r="20" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -5029,7 +5259,7 @@
     </row>
     <row r="21" spans="1:18" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" s="33"/>
       <c r="C21" s="33"/>
@@ -5051,7 +5281,7 @@
     </row>
     <row r="22" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -5073,7 +5303,7 @@
     </row>
     <row r="23" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
@@ -5095,7 +5325,7 @@
     </row>
     <row r="24" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -5117,7 +5347,7 @@
     </row>
     <row r="25" spans="1:18" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
@@ -5139,7 +5369,7 @@
     </row>
     <row r="26" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -5161,7 +5391,7 @@
     </row>
     <row r="27" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -5183,7 +5413,7 @@
     </row>
     <row r="28" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -5205,7 +5435,7 @@
     </row>
     <row r="29" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -5227,7 +5457,7 @@
     </row>
     <row r="30" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -5249,7 +5479,7 @@
     </row>
     <row r="31" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -5271,7 +5501,7 @@
     </row>
     <row r="32" spans="1:18" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="33"/>
@@ -5293,7 +5523,7 @@
     </row>
     <row r="33" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -5315,7 +5545,7 @@
     </row>
     <row r="34" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -5337,7 +5567,7 @@
     </row>
     <row r="35" spans="1:40" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" s="33"/>
       <c r="C35" s="33"/>
@@ -5359,7 +5589,7 @@
     </row>
     <row r="36" spans="1:40" s="5" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -5367,7 +5597,7 @@
     </row>
     <row r="37" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -5389,7 +5619,7 @@
     </row>
     <row r="38" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -5411,7 +5641,7 @@
     </row>
     <row r="39" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -5433,7 +5663,7 @@
     </row>
     <row r="40" spans="1:40" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -5455,7 +5685,7 @@
     </row>
     <row r="41" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -5477,7 +5707,7 @@
     </row>
     <row r="42" spans="1:40" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" s="33"/>
       <c r="C42" s="33"/>
@@ -5499,7 +5729,7 @@
     </row>
     <row r="43" spans="1:40" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -5521,7 +5751,7 @@
     </row>
     <row r="44" spans="1:40" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
@@ -5543,7 +5773,7 @@
     </row>
     <row r="45" spans="1:40" s="6" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -5587,7 +5817,7 @@
     </row>
     <row r="46" spans="1:40" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -5609,7 +5839,7 @@
     </row>
     <row r="47" spans="1:40" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -5631,7 +5861,7 @@
     </row>
     <row r="48" spans="1:40" s="6" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -5675,7 +5905,7 @@
     </row>
     <row r="49" spans="1:18" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="33" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B49" s="33"/>
       <c r="C49" s="33"/>
@@ -5697,7 +5927,7 @@
     </row>
     <row r="50" spans="1:18" s="4" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -5719,7 +5949,7 @@
     </row>
     <row r="51" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -5741,7 +5971,7 @@
     </row>
     <row r="52" spans="1:18" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B52" s="33"/>
       <c r="C52" s="33"/>
@@ -5763,7 +5993,7 @@
     </row>
     <row r="53" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -5785,7 +6015,7 @@
     </row>
     <row r="54" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -5807,7 +6037,7 @@
     </row>
     <row r="55" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
@@ -5829,7 +6059,7 @@
     </row>
     <row r="56" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -5851,7 +6081,7 @@
     </row>
     <row r="57" spans="1:18" s="4" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B57" s="33"/>
       <c r="C57" s="33"/>
@@ -5873,7 +6103,7 @@
     </row>
     <row r="58" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
@@ -5895,7 +6125,7 @@
     </row>
     <row r="59" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -5917,7 +6147,7 @@
     </row>
     <row r="60" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -5939,7 +6169,7 @@
     </row>
     <row r="61" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -5961,7 +6191,7 @@
     </row>
     <row r="62" spans="1:18" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" s="33"/>
       <c r="C62" s="33"/>
@@ -5983,7 +6213,7 @@
     </row>
     <row r="63" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -6005,7 +6235,7 @@
     </row>
     <row r="64" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
@@ -6027,7 +6257,7 @@
     </row>
     <row r="65" spans="1:18" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A65" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -6049,7 +6279,7 @@
     </row>
     <row r="66" spans="1:18" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A66" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
@@ -6071,7 +6301,7 @@
     </row>
     <row r="67" spans="1:18" s="4" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A67" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
@@ -6093,7 +6323,7 @@
     </row>
     <row r="68" spans="1:18" s="4" customFormat="1" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
@@ -6114,10 +6344,10 @@
       <c r="R68" s="3"/>
     </row>
     <row r="69" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="68"/>
-      <c r="B69" s="69"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="70"/>
+      <c r="A69" s="62"/>
+      <c r="B69" s="63"/>
+      <c r="C69" s="63"/>
+      <c r="D69" s="64"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -6134,10 +6364,10 @@
       <c r="R69" s="1"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A70" s="57"/>
-      <c r="B70" s="57"/>
-      <c r="C70" s="57"/>
-      <c r="D70" s="57"/>
+      <c r="A70" s="70"/>
+      <c r="B70" s="70"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="70"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -7086,18 +7316,2148 @@
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="A1:D1048576">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"Partially passed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22:D24 D26:D34 D63:D68 D36:D61 D18:D20 D4:D12 D13:D16" xr:uid="{CB7374B2-3267-1E4F-8438-AC26C496CAB2}">
+      <formula1>"Pass,Fail,Partially passed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="61" fitToHeight="0" orientation="landscape" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{626204B4-C67D-764D-AED7-875BF430344F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AN120"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="75" style="8" customWidth="1"/>
+    <col min="2" max="3" width="60.83203125" style="17" customWidth="1"/>
+    <col min="4" max="4" width="27.83203125" style="35" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:39" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="43"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+    </row>
+    <row r="2" spans="1:39" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="61" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:39" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+    </row>
+    <row r="4" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+    </row>
+    <row r="5" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+    </row>
+    <row r="6" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="1:39" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:39" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:39" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="1:18" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="1:18" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="1:18" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="1:18" s="5" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="34"/>
+    </row>
+    <row r="30" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="1:40" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="1:40" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="1:40" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="36" spans="1:40" s="6" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
+      <c r="AA36" s="5"/>
+      <c r="AB36" s="5"/>
+      <c r="AC36" s="5"/>
+      <c r="AD36" s="5"/>
+      <c r="AE36" s="5"/>
+      <c r="AF36" s="5"/>
+      <c r="AG36" s="5"/>
+      <c r="AH36" s="5"/>
+      <c r="AI36" s="5"/>
+      <c r="AJ36" s="5"/>
+      <c r="AK36" s="5"/>
+      <c r="AL36" s="5"/>
+      <c r="AM36" s="5"/>
+      <c r="AN36" s="5"/>
+    </row>
+    <row r="37" spans="1:40" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+    </row>
+    <row r="38" spans="1:40" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+    </row>
+    <row r="39" spans="1:40" s="4" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="1:40" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="33"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="1:40" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="1:40" s="4" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="33"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="1:18" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="62"/>
+      <c r="B51" s="63"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A52" s="70"/>
+      <c r="B52" s="70"/>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A53" s="14"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A54" s="15"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="36"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="1"/>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B61" s="19"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="36"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="36"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="1"/>
+      <c r="R62" s="1"/>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
+      <c r="R63" s="1"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="1"/>
+      <c r="R64" s="1"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="1"/>
+      <c r="R66" s="1"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="36"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="1"/>
+      <c r="R67" s="1"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B70" s="19"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B72" s="19"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="1"/>
+      <c r="R73" s="1"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
+      <c r="P74" s="1"/>
+      <c r="Q74" s="1"/>
+      <c r="R74" s="1"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1"/>
+      <c r="R75" s="1"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B77" s="19"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="36"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
+      <c r="R77" s="1"/>
+    </row>
+    <row r="78" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B78" s="19"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
+      <c r="P78" s="1"/>
+      <c r="Q78" s="1"/>
+      <c r="R78" s="1"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B79" s="19"/>
+      <c r="C79" s="19"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1"/>
+      <c r="O79" s="1"/>
+      <c r="P79" s="1"/>
+      <c r="Q79" s="1"/>
+      <c r="R79" s="1"/>
+    </row>
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B80" s="19"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+      <c r="N80" s="1"/>
+      <c r="O80" s="1"/>
+      <c r="P80" s="1"/>
+      <c r="Q80" s="1"/>
+      <c r="R80" s="1"/>
+    </row>
+    <row r="81" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B81" s="19"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="36"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="O81" s="1"/>
+      <c r="P81" s="1"/>
+      <c r="Q81" s="1"/>
+      <c r="R81" s="1"/>
+    </row>
+    <row r="82" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B82" s="19"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="36"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="1"/>
+      <c r="R82" s="1"/>
+    </row>
+    <row r="83" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B83" s="19"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="36"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
+      <c r="P83" s="1"/>
+      <c r="Q83" s="1"/>
+      <c r="R83" s="1"/>
+    </row>
+    <row r="84" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B84" s="19"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+      <c r="N84" s="1"/>
+      <c r="O84" s="1"/>
+      <c r="P84" s="1"/>
+      <c r="Q84" s="1"/>
+      <c r="R84" s="1"/>
+    </row>
+    <row r="85" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B85" s="19"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="36"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+      <c r="O85" s="1"/>
+      <c r="P85" s="1"/>
+      <c r="Q85" s="1"/>
+      <c r="R85" s="1"/>
+    </row>
+    <row r="86" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B86" s="19"/>
+      <c r="C86" s="19"/>
+      <c r="D86" s="36"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
+      <c r="O86" s="1"/>
+      <c r="P86" s="1"/>
+      <c r="Q86" s="1"/>
+      <c r="R86" s="1"/>
+    </row>
+    <row r="87" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B87" s="19"/>
+      <c r="C87" s="19"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+      <c r="N87" s="1"/>
+      <c r="O87" s="1"/>
+      <c r="P87" s="1"/>
+      <c r="Q87" s="1"/>
+      <c r="R87" s="1"/>
+    </row>
+    <row r="88" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B88" s="19"/>
+      <c r="C88" s="19"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
+      <c r="O88" s="1"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1"/>
+      <c r="R88" s="1"/>
+    </row>
+    <row r="89" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B89" s="19"/>
+      <c r="C89" s="19"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1"/>
+      <c r="N89" s="1"/>
+      <c r="O89" s="1"/>
+      <c r="P89" s="1"/>
+      <c r="Q89" s="1"/>
+      <c r="R89" s="1"/>
+    </row>
+    <row r="90" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B90" s="19"/>
+      <c r="C90" s="19"/>
+      <c r="D90" s="36"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+      <c r="N90" s="1"/>
+      <c r="O90" s="1"/>
+      <c r="P90" s="1"/>
+      <c r="Q90" s="1"/>
+      <c r="R90" s="1"/>
+    </row>
+    <row r="91" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B91" s="19"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="36"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+      <c r="N91" s="1"/>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1"/>
+      <c r="R91" s="1"/>
+    </row>
+    <row r="92" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B92" s="19"/>
+      <c r="C92" s="19"/>
+      <c r="D92" s="36"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+      <c r="O92" s="1"/>
+      <c r="P92" s="1"/>
+      <c r="Q92" s="1"/>
+      <c r="R92" s="1"/>
+    </row>
+    <row r="93" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B93" s="19"/>
+      <c r="C93" s="19"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+    </row>
+    <row r="94" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B94" s="19"/>
+      <c r="C94" s="19"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+      <c r="O94" s="1"/>
+      <c r="P94" s="1"/>
+      <c r="Q94" s="1"/>
+      <c r="R94" s="1"/>
+    </row>
+    <row r="95" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B95" s="19"/>
+      <c r="C95" s="19"/>
+      <c r="D95" s="36"/>
+    </row>
+    <row r="96" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="B96" s="19"/>
+      <c r="C96" s="19"/>
+      <c r="D96" s="36"/>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B97" s="19"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="36"/>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B98" s="19"/>
+      <c r="C98" s="19"/>
+      <c r="D98" s="36"/>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B99" s="19"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="36"/>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B100" s="19"/>
+      <c r="C100" s="19"/>
+      <c r="D100" s="36"/>
+    </row>
+    <row r="101" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B101" s="19"/>
+      <c r="C101" s="19"/>
+      <c r="D101" s="36"/>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B102" s="19"/>
+      <c r="C102" s="19"/>
+      <c r="D102" s="36"/>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B103" s="19"/>
+      <c r="C103" s="19"/>
+      <c r="D103" s="36"/>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B104" s="19"/>
+      <c r="C104" s="19"/>
+      <c r="D104" s="36"/>
+    </row>
+    <row r="105" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B105" s="19"/>
+      <c r="C105" s="19"/>
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B106" s="19"/>
+      <c r="C106" s="19"/>
+      <c r="D106" s="36"/>
+    </row>
+    <row r="107" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B107" s="19"/>
+      <c r="C107" s="19"/>
+      <c r="D107" s="36"/>
+    </row>
+    <row r="108" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B108" s="19"/>
+      <c r="C108" s="19"/>
+      <c r="D108" s="36"/>
+    </row>
+    <row r="109" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B109" s="19"/>
+      <c r="C109" s="19"/>
+      <c r="D109" s="36"/>
+    </row>
+    <row r="110" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B110" s="19"/>
+      <c r="C110" s="19"/>
+      <c r="D110" s="36"/>
+    </row>
+    <row r="111" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B111" s="19"/>
+      <c r="C111" s="19"/>
+      <c r="D111" s="36"/>
+    </row>
+    <row r="112" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B112" s="19"/>
+      <c r="C112" s="19"/>
+      <c r="D112" s="36"/>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B113" s="19"/>
+      <c r="C113" s="19"/>
+      <c r="D113" s="36"/>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B114" s="19"/>
+      <c r="C114" s="19"/>
+      <c r="D114" s="36"/>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B115" s="19"/>
+      <c r="C115" s="19"/>
+      <c r="D115" s="36"/>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B116" s="19"/>
+      <c r="C116" s="19"/>
+      <c r="D116" s="36"/>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B117" s="19"/>
+      <c r="C117" s="19"/>
+      <c r="D117" s="36"/>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B118" s="19"/>
+      <c r="C118" s="19"/>
+      <c r="D118" s="36"/>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B119" s="19"/>
+      <c r="C119" s="19"/>
+      <c r="D119" s="36"/>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B120" s="19"/>
+      <c r="C120" s="19"/>
+      <c r="D120" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A52:D52"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:D1048576">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Partially passed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14:D17 D9:D12 D4:D7 D19:D27 D29:D50" xr:uid="{AA484181-A293-224F-A3D2-103D8D97479E}">
       <formula1>"Pass,Fail,Partially passed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7119,15 +9479,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007109CA6D1BBE11448D524EF4021B9A18" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4a2dcb2384401c582d81c97af0274d8d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d3cdee01-5911-4841-93a2-01f79d1ce2bf" xmlns:ns3="a3f86f60-5163-4434-ba4a-73f68b170085" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="35f524b1b6305ae5c99c00bf07bfe9fe" ns2:_="" ns3:_="">
     <xsd:import namespace="d3cdee01-5911-4841-93a2-01f79d1ce2bf"/>
@@ -7334,6 +9685,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A20D01FA-78BD-4420-BAF6-4011C2F707E6}">
   <ds:schemaRefs>
@@ -7355,14 +9715,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF5CF93-F330-4D34-8EA3-3A4319739D9D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C638C731-6A9D-4DDE-AA13-00C053643AA6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7379,4 +9731,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF5CF93-F330-4D34-8EA3-3A4319739D9D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>